--- a/data/MAX_STORE_Google_Sheet_Template.xlsx
+++ b/data/MAX_STORE_Google_Sheet_Template.xlsx
@@ -8,16 +8,28 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrderItems" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviews" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notifications" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sellers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sellers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrderItems" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviews" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notifications" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Withdrawals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Users'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sellers'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Products'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Orders'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OrderItems'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Reviews'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Categories'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Notifications'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Withdrawals'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Support'!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -447,7 +459,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Password Hash</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -467,6 +479,59 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Ticket ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>User ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Created At</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Updated At</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -477,62 +542,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Product ID</t>
+          <t>Seller ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Seller ID</t>
+          <t>User ID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Store Name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Image</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
           <t>Created At</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Seller ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Created At</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Updated At</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -599,52 +717,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Order ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Seller ID</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -661,7 +734,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Review ID</t>
+          <t>Order ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -671,31 +744,79 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>User ID</t>
+          <t>Seller ID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Created At</t>
+          <t>Qty</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Review ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>User ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Created At</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -945,52 +1066,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Notification ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>User ID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Created At</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:B1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1007,7 +1083,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Seller ID</t>
+          <t>Notification ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1017,17 +1093,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Store Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -1037,6 +1113,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1078,6 +1155,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>